--- a/output/datacenters_matched.xlsx
+++ b/output/datacenters_matched.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP320"/>
+  <dimension ref="A1:AM320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,32 +599,17 @@
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>research_year_x</t>
+          <t>research_year</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>year_basis_used_x</t>
+          <t>year_basis_used</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>year_source_link_x</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>research_year_y</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>year_basis_used_y</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>year_source_link_y</t>
+          <t>year_source_link</t>
         </is>
       </c>
     </row>
@@ -778,19 +763,6 @@
           <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,19 +910,6 @@
         </is>
       </c>
       <c r="AM3" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-jacksonville-road</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/microsoft-jacksonville-road</t>
         </is>
@@ -1092,19 +1051,6 @@
           <t>https://baxtel.com/data-center/equinix-manassas-dc14</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>2004</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-manassas-dc14</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1256,19 +1202,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-7-iad-11-iad-24-5e845654</t>
         </is>
       </c>
-      <c r="AN5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-7-iad-11-iad-24-5e845654</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1420,19 +1353,6 @@
           <t>https://baxtel.com/data-center/amazon-iad24</t>
         </is>
       </c>
-      <c r="AN6" t="n">
-        <v>2012</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad24</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1584,19 +1504,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-7-iad-11-iad-24-5e845654</t>
         </is>
       </c>
-      <c r="AN7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-7-iad-11-iad-24-5e845654</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1744,19 +1651,6 @@
           <t>https://baxtel.com/data-center/8217-linton-hall-va4-digital-realty</t>
         </is>
       </c>
-      <c r="AN8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/8217-linton-hall-va4-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1912,19 +1806,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2080,19 +1961,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2248,19 +2116,6 @@
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
       </c>
-      <c r="AN11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2416,19 +2271,6 @@
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
       </c>
-      <c r="AN12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2584,19 +2426,6 @@
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
       </c>
-      <c r="AN13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2752,19 +2581,6 @@
           <t>https://baxtel.com/data-center/stack-northern-virginia</t>
         </is>
       </c>
-      <c r="AN14" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/stack-northern-virginia</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2916,19 +2732,6 @@
           <t>https://baxtel.com/data-center/1780-business-center-drive-va3-digital-realty</t>
         </is>
       </c>
-      <c r="AN15" t="n">
-        <v>2001</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/1780-business-center-drive-va3-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3080,19 +2883,6 @@
           <t>https://baxtel.com/data-center/lincoln-rackhouse-1807-michael-faraday</t>
         </is>
       </c>
-      <c r="AN16" t="n">
-        <v>2008</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/lincoln-rackhouse-1807-michael-faraday</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3244,19 +3034,6 @@
           <t>https://baxtel.com/data-center/coresite-reston-campus-va1</t>
         </is>
       </c>
-      <c r="AN17" t="n">
-        <v>2006</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/coresite-reston-campus-va1</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3404,19 +3181,6 @@
         </is>
       </c>
       <c r="AM18" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/coresite-reston-va3</t>
-        </is>
-      </c>
-      <c r="AN18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/coresite-reston-va3</t>
         </is>
@@ -3556,19 +3320,6 @@
           <t>https://baxtel.com/data-center/8100-boone-digital-realty</t>
         </is>
       </c>
-      <c r="AN19" t="n">
-        <v>1992</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/8100-boone-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3712,19 +3463,6 @@
           <t>https://baxtel.com/news/equinix-completes-acquisition-of-29-data-centers-from-verizon-press-release</t>
         </is>
       </c>
-      <c r="AN20" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/news/equinix-completes-acquisition-of-29-data-centers-from-verizon-press-release</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3876,19 +3614,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
         </is>
       </c>
-      <c r="AN21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4032,19 +3757,6 @@
           <t>https://cdn.baxtel.com/data-center/copt-dc-6/files/COPT-DC6_brochure-pdf</t>
         </is>
       </c>
-      <c r="AN22" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>https://cdn.baxtel.com/data-center/copt-dc-6/files/COPT-DC6_brochure-pdf</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4188,19 +3900,6 @@
           <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
         </is>
       </c>
-      <c r="AN23" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4356,19 +4055,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc2</t>
         </is>
       </c>
-      <c r="AN24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc2</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4524,19 +4210,6 @@
           <t>https://baxtel.com/data-center/h5-ashburn</t>
         </is>
       </c>
-      <c r="AN25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/h5-ashburn</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4684,19 +4357,6 @@
           <t>https://baxtel.com/data-center/lumen-mclean-1</t>
         </is>
       </c>
-      <c r="AN26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/lumen-mclean-1</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4848,19 +4508,6 @@
           <t>https://baxtel.com/data-center/databank-mclean-iad2</t>
         </is>
       </c>
-      <c r="AN27" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/databank-mclean-iad2</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5008,19 +4655,6 @@
           <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
         </is>
       </c>
-      <c r="AN28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5168,19 +4802,6 @@
           <t>https://baxtel.com/data-center/flexential-richmond-data-center</t>
         </is>
       </c>
-      <c r="AN29" t="n">
-        <v>2001</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/flexential-richmond-data-center</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5332,19 +4953,6 @@
           <t>https://baxtel.com/data-center/amazon-iad9</t>
         </is>
       </c>
-      <c r="AN30" t="n">
-        <v>2009</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad9</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5488,19 +5096,6 @@
           <t>https://baxtel.com/data-center/amazon-iad1</t>
         </is>
       </c>
-      <c r="AN31" t="n">
-        <v>2006</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad1</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5648,19 +5243,6 @@
         </is>
       </c>
       <c r="AM32" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad1</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>2006</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/amazon-iad1</t>
         </is>
@@ -5802,19 +5384,6 @@
           <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
         </is>
       </c>
-      <c r="AN33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5952,19 +5521,6 @@
           <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
         </is>
       </c>
-      <c r="AN34" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6102,19 +5658,6 @@
           <t>https://baxtel.com/data-center/element-critical-va1</t>
         </is>
       </c>
-      <c r="AN35" t="n">
-        <v>2016</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/element-critical-va1</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6270,19 +5813,6 @@
           <t>https://baxtel.com/data-center/centersquare-dulles-iad3</t>
         </is>
       </c>
-      <c r="AN36" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-dulles-iad3</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6438,19 +5968,6 @@
           <t>https://baxtel.com/data-center/centersquare-iad2-a</t>
         </is>
       </c>
-      <c r="AN37" t="n">
-        <v>1999</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-iad2-a</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6604,19 +6121,6 @@
           <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-iv</t>
         </is>
       </c>
-      <c r="AN38" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-iv</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6772,19 +6276,6 @@
           <t>https://baxtel.com/data-center/centersquare-iad2-b</t>
         </is>
       </c>
-      <c r="AN39" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-iad2-b</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6940,19 +6431,6 @@
           <t>https://baxtel.com/data-center/44480-hastings-acc4-digital-realty</t>
         </is>
       </c>
-      <c r="AN40" t="n">
-        <v>2007</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/44480-hastings-acc4-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7108,19 +6586,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc1-dda903a5-7026-47aa-ad51-66d8ae59a21e</t>
         </is>
       </c>
-      <c r="AN41" t="n">
-        <v>1998</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc1-dda903a5-7026-47aa-ad51-66d8ae59a21e</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7276,19 +6741,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc5</t>
         </is>
       </c>
-      <c r="AN42" t="n">
-        <v>2007</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc5</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -7444,19 +6896,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc11</t>
         </is>
       </c>
-      <c r="AN43" t="n">
-        <v>2013</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP43" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc11</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7612,19 +7051,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc3</t>
         </is>
       </c>
-      <c r="AN44" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc3</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7778,19 +7204,6 @@
           <t>https://baxtel.com/data-center/44520-hastings-acc3-digital-realty</t>
         </is>
       </c>
-      <c r="AN45" t="n">
-        <v>2001</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/44520-hastings-acc3-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7946,19 +7359,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
         </is>
       </c>
-      <c r="AN46" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8114,19 +7514,6 @@
           <t>https://baxtel.com/data-center/amazon-iad12</t>
         </is>
       </c>
-      <c r="AN47" t="n">
-        <v>2011</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP47" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad12</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8276,19 +7663,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
         </is>
       </c>
-      <c r="AN48" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8444,19 +7818,6 @@
           <t>https://baxtel.com/data-center/44521-hastings-acc5-digital-realty</t>
         </is>
       </c>
-      <c r="AN49" t="n">
-        <v>2009</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/44521-hastings-acc5-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8612,19 +7973,6 @@
           <t>https://baxtel.com/data-center/44461-chilum-acc6-digital-realty</t>
         </is>
       </c>
-      <c r="AN50" t="n">
-        <v>2011</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/44461-chilum-acc6-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8774,19 +8122,6 @@
           <t>https://baxtel.com/data-center/lumen-mclean-1</t>
         </is>
       </c>
-      <c r="AN51" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/lumen-mclean-1</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8942,19 +8277,6 @@
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
       </c>
-      <c r="AN52" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -9110,19 +8432,6 @@
           <t>https://baxtel.com/data-center/ntt-va1</t>
         </is>
       </c>
-      <c r="AN53" t="n">
-        <v>1998</v>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va1</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -9278,19 +8587,6 @@
           <t>https://baxtel.com/data-center/equinix-dc13</t>
         </is>
       </c>
-      <c r="AN54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP54" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-dc13</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -9446,19 +8742,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN55" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -9610,19 +8893,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN56" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -9778,19 +9048,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN57" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9942,19 +9199,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN58" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP58" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -10110,19 +9354,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP59" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -10282,19 +9513,6 @@
           <t>https://baxtel.com/data-center/databank-ashburn-iad1</t>
         </is>
       </c>
-      <c r="AN60" t="n">
-        <v>2009</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/databank-ashburn-iad1</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -10446,19 +9664,6 @@
           <t>https://baxtel.com/data-center/databank-ashburn-iad1</t>
         </is>
       </c>
-      <c r="AN61" t="n">
-        <v>2009</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP61" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/databank-ashburn-iad1</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -10608,19 +9813,6 @@
           <t>https://baxtel.com/data-center/equinix-vienna-dc7</t>
         </is>
       </c>
-      <c r="AN62" t="n">
-        <v>2002</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-vienna-dc7</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -10762,19 +9954,6 @@
           <t>https://baxtel.com/data-center/element-critical-va1</t>
         </is>
       </c>
-      <c r="AN63" t="n">
-        <v>2016</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/element-critical-va1</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -10922,19 +10101,6 @@
           <t>https://baxtel.com/data-center/visa-eastern-us-ashburn</t>
         </is>
       </c>
-      <c r="AN64" t="n">
-        <v>2010</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/visa-eastern-us-ashburn</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -11094,19 +10260,6 @@
           <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-i-ii-iii</t>
         </is>
       </c>
-      <c r="AN65" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP65" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-i-ii-iii</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -11258,19 +10411,6 @@
           <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-v</t>
         </is>
       </c>
-      <c r="AN66" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP66" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-northern-virginia-sterling-v</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -11418,19 +10558,6 @@
           <t>https://baxtel.com/data-center/equinix-culpeper-campus</t>
         </is>
       </c>
-      <c r="AN67" t="n">
-        <v>2009</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-culpeper-campus</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -11582,19 +10709,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc10</t>
         </is>
       </c>
-      <c r="AN68" t="n">
-        <v>2012</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc10</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -11746,19 +10860,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN69" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP69" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -11910,19 +11011,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN70" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP70" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -12074,19 +11162,6 @@
         </is>
       </c>
       <c r="AM71" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
-        </is>
-      </c>
-      <c r="AN71" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP71" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
         </is>
@@ -12228,19 +11303,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
         </is>
       </c>
-      <c r="AN72" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -12396,19 +11458,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
         </is>
       </c>
-      <c r="AN73" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -12564,19 +11613,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
         </is>
       </c>
-      <c r="AN74" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP74" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -12732,19 +11768,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
         </is>
       </c>
-      <c r="AN75" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP75" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -12900,19 +11923,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
         </is>
       </c>
-      <c r="AN76" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -13064,19 +12074,6 @@
           <t>https://baxtel.com/data-center/amazon-iad14</t>
         </is>
       </c>
-      <c r="AN77" t="n">
-        <v>2012</v>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad14</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -13228,19 +12225,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
         </is>
       </c>
-      <c r="AN78" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP78" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -13388,19 +12372,6 @@
         </is>
       </c>
       <c r="AM79" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
-        </is>
-      </c>
-      <c r="AN79" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
         </is>
@@ -13546,19 +12517,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
         </is>
       </c>
-      <c r="AN80" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP80" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-12-iad-15-iad-16-iad--dad0396f</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -13714,19 +12672,6 @@
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
       </c>
-      <c r="AN81" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -13878,19 +12823,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN82" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -14046,19 +12978,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN83" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP83" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -14214,19 +13133,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN84" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP84" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -14370,19 +13276,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
         </is>
       </c>
-      <c r="AN85" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP85" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -14538,19 +13431,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
         </is>
       </c>
-      <c r="AN86" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP86" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-51-iad-56-iad-88-iad--1cdb8275</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -14702,19 +13582,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
         </is>
       </c>
-      <c r="AN87" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP87" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -14866,19 +13733,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
         </is>
       </c>
-      <c r="AN88" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP88" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -15034,19 +13888,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
         </is>
       </c>
-      <c r="AN89" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP89" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -15202,19 +14043,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
         </is>
       </c>
-      <c r="AN90" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -15370,19 +14198,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN91" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -15538,19 +14353,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN92" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP92" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -15706,19 +14508,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN93" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP93" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -15874,19 +14663,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
         </is>
       </c>
-      <c r="AN94" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP94" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-50-iad-60-iad-71-iad--8aa2285d</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -16042,19 +14818,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc12</t>
         </is>
       </c>
-      <c r="AN95" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc12</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -16210,19 +14973,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN96" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP96" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -16378,19 +15128,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN97" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP97" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -16546,19 +15283,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN98" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP98" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -16714,19 +15438,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN99" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -16882,19 +15593,6 @@
           <t>https://baxtel.com/data-center/ntt-va1</t>
         </is>
       </c>
-      <c r="AN100" t="n">
-        <v>1998</v>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP100" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va1</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -17050,19 +15748,6 @@
           <t>https://baxtel.com/data-center/21625-gresham-acc7-digital-realty</t>
         </is>
       </c>
-      <c r="AN101" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP101" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/21625-gresham-acc7-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -17214,19 +15899,6 @@
           <t>https://baxtel.com/data-center/ntt-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN102" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -17386,19 +16058,6 @@
           <t>https://baxtel.com/data-center/ntt-va3</t>
         </is>
       </c>
-      <c r="AN103" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va3</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -17554,19 +16213,6 @@
           <t>https://baxtel.com/data-center/21745-sir-timothy-acc9-digital-realty</t>
         </is>
       </c>
-      <c r="AN104" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP104" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/21745-sir-timothy-acc9-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -17718,19 +16364,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN105" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP105" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -17874,19 +16507,6 @@
           <t>https://baxtel.com/data-center/microsoft-boydton-va</t>
         </is>
       </c>
-      <c r="AN106" t="n">
-        <v>2013</v>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP106" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-boydton-va</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -18030,19 +16650,6 @@
           <t>https://baxtel.com/data-center/boa-sandston</t>
         </is>
       </c>
-      <c r="AN107" t="n">
-        <v>2015</v>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/boa-sandston</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -18198,19 +16805,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
         </is>
       </c>
-      <c r="AN108" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -18366,19 +16960,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
         </is>
       </c>
-      <c r="AN109" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -18534,19 +17115,6 @@
           <t>https://baxtel.com/data-center/google-arcola-2</t>
         </is>
       </c>
-      <c r="AN110" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-arcola-2</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -18702,19 +17270,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
         </is>
       </c>
-      <c r="AN111" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP111" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -18866,19 +17421,6 @@
         </is>
       </c>
       <c r="AM112" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
-        </is>
-      </c>
-      <c r="AN112" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
         </is>
@@ -19024,19 +17566,6 @@
           <t>https://baxtel.com/data-center/aligned-ashburn</t>
         </is>
       </c>
-      <c r="AN113" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/aligned-ashburn</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -19178,19 +17707,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-1</t>
         </is>
       </c>
-      <c r="AN114" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP114" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-1</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -19328,19 +17844,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
         </is>
       </c>
-      <c r="AN115" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP115" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-14-iad-52-iad-59-6b3f0f4e</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -19492,19 +17995,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
         </is>
       </c>
-      <c r="AN116" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP116" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -19648,19 +18138,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
         </is>
       </c>
-      <c r="AN117" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP117" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-57-iad-58amazon-data--8884432e</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -19812,19 +18289,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
         </is>
       </c>
-      <c r="AN118" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP118" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -19966,19 +18430,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
         </is>
       </c>
-      <c r="AN119" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -20130,19 +18581,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-1</t>
         </is>
       </c>
-      <c r="AN120" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP120" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-1</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -20298,19 +18736,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN121" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP121" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -20466,19 +18891,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN122" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -20634,19 +19046,6 @@
           <t>https://baxtel.com/data-center/21744-sir-timothy-drive-acc10</t>
         </is>
       </c>
-      <c r="AN123" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP123" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/21744-sir-timothy-drive-acc10</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -20792,19 +19191,6 @@
           <t>https://baxtel.com/data-center/sentinel-cloud-plaza-sterling-va</t>
         </is>
       </c>
-      <c r="AN124" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/sentinel-cloud-plaza-sterling-va</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -20960,19 +19346,6 @@
           <t>https://baxtel.com/data-center/vantage-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN125" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/vantage-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -21128,19 +19501,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
         </is>
       </c>
-      <c r="AN126" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -21296,19 +19656,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
         </is>
       </c>
-      <c r="AN127" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -21464,19 +19811,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
         </is>
       </c>
-      <c r="AN128" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-90-iad-91-iad-92-d3c8ee4d</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -21632,19 +19966,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-144-iad-145-393425b0</t>
         </is>
       </c>
-      <c r="AN129" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP129" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-144-iad-145-393425b0</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -21800,19 +20121,6 @@
           <t>https://baxtel.com/data-center/cyrusone-sterling-viii</t>
         </is>
       </c>
-      <c r="AN130" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP130" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-sterling-viii</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -21968,19 +20276,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN131" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -22136,19 +20431,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN132" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -22304,19 +20586,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-114-iad-115-19d2cc2c</t>
         </is>
       </c>
-      <c r="AN133" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-114-iad-115-19d2cc2c</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -22472,19 +20741,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-114-iad-115-19d2cc2c</t>
         </is>
       </c>
-      <c r="AN134" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-114-iad-115-19d2cc2c</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -22640,19 +20896,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
         </is>
       </c>
-      <c r="AN135" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -22808,19 +21051,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
         </is>
       </c>
-      <c r="AN136" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -22972,19 +21202,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN137" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -23128,19 +21345,6 @@
         </is>
       </c>
       <c r="AM138" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-richmond-i-dc6</t>
-        </is>
-      </c>
-      <c r="AN138" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/qts-richmond-i-dc6</t>
         </is>
@@ -23280,19 +21484,6 @@
           <t>https://baxtel.com/data-center/sabey-intergate-ashburn-building-a</t>
         </is>
       </c>
-      <c r="AN139" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/sabey-intergate-ashburn-building-a</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -23444,19 +21635,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN140" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -23608,19 +21786,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN141" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -23768,19 +21933,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
         </is>
       </c>
-      <c r="AN142" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -23936,19 +22088,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-144-iad-145-393425b0</t>
         </is>
       </c>
-      <c r="AN143" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-144-iad-145-393425b0</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -24104,19 +22243,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-116-iad-117-ceb841a9</t>
         </is>
       </c>
-      <c r="AN144" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-116-iad-117-ceb841a9</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -24272,19 +22398,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-116-iad-117-ceb841a9</t>
         </is>
       </c>
-      <c r="AN145" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP145" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-116-iad-117-ceb841a9</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -24436,19 +22549,6 @@
           <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
         </is>
       </c>
-      <c r="AN146" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -24604,19 +22704,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN147" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -24772,19 +22859,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN148" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP148" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -24936,19 +23010,6 @@
           <t>https://baxtel.com/data-center/aligned-ashburn</t>
         </is>
       </c>
-      <c r="AN149" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP149" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/aligned-ashburn</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -25104,19 +23165,6 @@
           <t>https://baxtel.com/data-center/equinix-dc15</t>
         </is>
       </c>
-      <c r="AN150" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP150" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-dc15</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -25268,19 +23316,6 @@
           <t>https://baxtel.com/data-center/sabey-intergate-ashburn-building-a</t>
         </is>
       </c>
-      <c r="AN151" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP151" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/sabey-intergate-ashburn-building-a</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -25440,19 +23475,6 @@
           <t>https://baxtel.com/data-center/ntt-va5</t>
         </is>
       </c>
-      <c r="AN152" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va5</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -25612,19 +23634,6 @@
           <t>https://baxtel.com/data-center/ntt-va4</t>
         </is>
       </c>
-      <c r="AN153" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP153" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va4</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -25780,19 +23789,6 @@
           <t>https://baxtel.com/data-center/cloudhq-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN154" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -25948,19 +23944,6 @@
           <t>https://baxtel.com/data-center/cloudhq-lc2</t>
         </is>
       </c>
-      <c r="AN155" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP155" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-lc2</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -26116,19 +24099,6 @@
           <t>https://www.datacenter.fyi/project/vadata-inc-iad-146-iad-147-acc2ffed</t>
         </is>
       </c>
-      <c r="AN156" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/vadata-inc-iad-146-iad-147-acc2ffed</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -26284,19 +24254,6 @@
           <t>https://baxtel.com/data-center/equinix-dc21</t>
         </is>
       </c>
-      <c r="AN157" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-dc21</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -26452,19 +24409,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
         </is>
       </c>
-      <c r="AN158" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -26620,19 +24564,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
         </is>
       </c>
-      <c r="AN159" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -26784,19 +24715,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
         </is>
       </c>
-      <c r="AN160" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-55-iad-64-iad-84-9666c549</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -26940,19 +24858,6 @@
         </is>
       </c>
       <c r="AM161" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/middletown-data-center</t>
-        </is>
-      </c>
-      <c r="AN161" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/middletown-data-center</t>
         </is>
@@ -27098,19 +25003,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN162" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -27266,19 +25158,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
         </is>
       </c>
-      <c r="AN163" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-10-iad-32-iad-98-iad--2c17f1bb</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -27426,19 +25305,6 @@
           <t>https://www.dbtdata.com/locations/harrisonburg-data-center/</t>
         </is>
       </c>
-      <c r="AN164" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>https://www.dbtdata.com/locations/harrisonburg-data-center/</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -27590,19 +25456,6 @@
           <t>https://baxtel.com/data-center/cloudhq-manassas-mcc1</t>
         </is>
       </c>
-      <c r="AN165" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-manassas-mcc1</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -27758,19 +25611,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN166" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP166" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -27926,19 +25766,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN167" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -28086,19 +25913,6 @@
           <t>https://baxtel.com/news/blackchamber-plans-to-develop-a-large-data-center-campus-in-northern-virginia</t>
         </is>
       </c>
-      <c r="AN168" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP168" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/news/blackchamber-plans-to-develop-a-large-data-center-campus-in-northern-virginia</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -28254,19 +26068,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN169" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP169" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -28422,19 +26223,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN170" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -28586,19 +26374,6 @@
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
       </c>
-      <c r="AN171" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -28750,19 +26525,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
         </is>
       </c>
-      <c r="AN172" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -28918,19 +26680,6 @@
           <t>https://baxtel.com/data-center/amazon-iad-175</t>
         </is>
       </c>
-      <c r="AN173" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad-175</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -29086,19 +26835,6 @@
           <t>https://www.datacenter.fyi/project/vadata-inc-iad-146-iad-147-acc2ffed</t>
         </is>
       </c>
-      <c r="AN174" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/vadata-inc-iad-146-iad-147-acc2ffed</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -29250,19 +26986,6 @@
           <t>https://baxtel.com/data-center/cyrusone-nva7</t>
         </is>
       </c>
-      <c r="AN175" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-nva7</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -29414,19 +27137,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
         </is>
       </c>
-      <c r="AN176" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -29578,19 +27288,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
         </is>
       </c>
-      <c r="AN177" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-163-164-174-b5656cce</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -29746,19 +27443,6 @@
           <t>https://baxtel.com/data-center/vantage-va12</t>
         </is>
       </c>
-      <c r="AN178" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/vantage-va12</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -29914,19 +27598,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN179" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -30082,19 +27753,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
         </is>
       </c>
-      <c r="AN180" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -30250,19 +27908,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
         </is>
       </c>
-      <c r="AN181" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP181" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-150-iad-151-iad-152-4d4981ec</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -30418,19 +28063,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
         </is>
       </c>
-      <c r="AN182" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP182" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-62-68-81-83-93-609-61-726685e7</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -30586,19 +28218,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN183" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -30754,19 +28373,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
         </is>
       </c>
-      <c r="AN184" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP184" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -30922,19 +28528,6 @@
           <t>https://baxtel.com/data-center/cyrusone-sterling-ix</t>
         </is>
       </c>
-      <c r="AN185" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cyrusone-sterling-ix</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -31082,19 +28675,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-va-2</t>
         </is>
       </c>
-      <c r="AN186" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP186" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-va-2</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -31242,19 +28822,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-northern-virginia-manassas</t>
         </is>
       </c>
-      <c r="AN187" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-northern-virginia-manassas</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -31406,19 +28973,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN188" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP188" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -31570,19 +29124,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN189" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP189" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -31734,19 +29275,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN190" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP190" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -31896,19 +29424,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
         </is>
       </c>
-      <c r="AN191" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP191" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -32058,19 +29573,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
         </is>
       </c>
-      <c r="AN192" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -32220,19 +29722,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
         </is>
       </c>
-      <c r="AN193" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP193" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -32384,19 +29873,6 @@
           <t>https://baxtel.com/data-center/cloudhq-mcc2</t>
         </is>
       </c>
-      <c r="AN194" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-mcc2</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -32544,19 +30020,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN195" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP195" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -32708,19 +30171,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
         </is>
       </c>
-      <c r="AN196" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -32872,19 +30322,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
         </is>
       </c>
-      <c r="AN197" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-73-iad-74-iad-602-iad-52ff662d</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -33040,19 +30477,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN198" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP198" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -33208,19 +30632,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN199" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -33368,19 +30779,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN200" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -33528,19 +30926,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN201" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP201" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -33688,19 +31073,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN202" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP202" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -33848,19 +31220,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN203" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -34004,19 +31363,6 @@
         </is>
       </c>
       <c r="AM204" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
-      <c r="AN204" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP204" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
@@ -34166,19 +31512,6 @@
           <t>https://baxtel.com/data-center/centersquare-iad2-a</t>
         </is>
       </c>
-      <c r="AN205" t="n">
-        <v>1999</v>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP205" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-iad2-a</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -34334,19 +31667,6 @@
           <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN206" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-loudoun-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -34498,19 +31818,6 @@
           <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
         </is>
       </c>
-      <c r="AN207" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP207" t="inlineStr">
-        <is>
-          <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -34662,19 +31969,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN208" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO208" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP208" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -34818,19 +32112,6 @@
         </is>
       </c>
       <c r="AM209" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
-      <c r="AN209" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP209" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
@@ -34972,19 +32253,6 @@
           <t>https://cdn.baxtel.com/data-center/copt-dc-6/files/COPT-DC6_brochure-pdf</t>
         </is>
       </c>
-      <c r="AN210" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AO210" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP210" t="inlineStr">
-        <is>
-          <t>https://cdn.baxtel.com/data-center/copt-dc-6/files/COPT-DC6_brochure-pdf</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -35136,19 +32404,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-132-iad-133-9e938968</t>
         </is>
       </c>
-      <c r="AN211" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP211" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-132-iad-133-9e938968</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -35300,19 +32555,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-132-iad-133-9e938968</t>
         </is>
       </c>
-      <c r="AN212" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-132-iad-133-9e938968</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -35464,19 +32706,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN213" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP213" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -35628,19 +32857,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN214" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP214" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -35792,19 +33008,6 @@
           <t>https://baxtel.com/data-center/aligned-iad02</t>
         </is>
       </c>
-      <c r="AN215" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP215" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/aligned-iad02</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -35952,19 +33155,6 @@
           <t>https://baxtel.com/data-center/qts-manassas-dc5</t>
         </is>
       </c>
-      <c r="AN216" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO216" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP216" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-manassas-dc5</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -36120,19 +33310,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN217" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -36288,19 +33465,6 @@
           <t>https://baxtel.com/data-center/equinix-dc16</t>
         </is>
       </c>
-      <c r="AN218" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP218" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-dc16</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -36448,19 +33612,6 @@
         </is>
       </c>
       <c r="AM219" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-iad11</t>
-        </is>
-      </c>
-      <c r="AN219" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP219" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/microsoft-iad11</t>
         </is>
@@ -36606,19 +33757,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN220" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP220" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -36760,19 +33898,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN221" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP221" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -36920,19 +34045,6 @@
           <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
         </is>
       </c>
-      <c r="AN222" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP222" t="inlineStr">
-        <is>
-          <t>https://cleanview.co/public/data-centers/virginia/758/henrico-data-center</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -37084,19 +34196,6 @@
           <t>https://baxtel.com/data-centers/coresite</t>
         </is>
       </c>
-      <c r="AN223" t="n">
-        <v>2008</v>
-      </c>
-      <c r="AO223" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP223" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-centers/coresite</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -37248,19 +34347,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN224" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP224" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -37412,19 +34498,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN225" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP225" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -37572,19 +34645,6 @@
           <t>https://baxtel.com/data-center/qts-manassas-dc1</t>
         </is>
       </c>
-      <c r="AN226" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-manassas-dc1</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -37736,19 +34796,6 @@
         </is>
       </c>
       <c r="AM227" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
-      <c r="AN227" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP227" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
@@ -37894,19 +34941,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
         </is>
       </c>
-      <c r="AN228" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP228" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-120-121-122-29fd53de</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -38062,19 +35096,6 @@
           <t>https://baxtel.com/data-center/google-arcola-2</t>
         </is>
       </c>
-      <c r="AN229" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP229" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-arcola-2</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -38230,19 +35251,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
         </is>
       </c>
-      <c r="AN230" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO230" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP230" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-140-141-143-e6feb70e</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -38398,19 +35406,6 @@
           <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
         </is>
       </c>
-      <c r="AN231" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP231" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/project/amazon-data-services-inc-iad-61-iad-63-iad-65-iad--fede1500</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -38562,19 +35557,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN232" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -38726,19 +35708,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN233" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO233" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP233" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -38890,19 +35859,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-shellhorn-dc2</t>
         </is>
       </c>
-      <c r="AN234" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO234" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP234" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-shellhorn-dc2</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -39054,19 +36010,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
         </is>
       </c>
-      <c r="AN235" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO235" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP235" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -39218,19 +36161,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
         </is>
       </c>
-      <c r="AN236" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP236" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -39382,19 +36312,6 @@
         </is>
       </c>
       <c r="AM237" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad-192</t>
-        </is>
-      </c>
-      <c r="AN237" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP237" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/amazon-iad-192</t>
         </is>
@@ -39544,19 +36461,6 @@
           <t>https://baxtel.com/data-center/ntt-ashburn-campus</t>
         </is>
       </c>
-      <c r="AN238" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP238" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-ashburn-campus</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -39716,19 +36620,6 @@
           <t>https://baxtel.com/data-center/ntt-va8</t>
         </is>
       </c>
-      <c r="AN239" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP239" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va8</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -39884,19 +36775,6 @@
           <t>https://baxtel.com/data-center/databank-ashburn-iad3</t>
         </is>
       </c>
-      <c r="AN240" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/databank-ashburn-iad3</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -40048,19 +36926,6 @@
         </is>
       </c>
       <c r="AM241" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/powerhouse-abx1</t>
-        </is>
-      </c>
-      <c r="AN241" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP241" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/powerhouse-abx1</t>
         </is>
@@ -40206,19 +37071,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc2</t>
         </is>
       </c>
-      <c r="AN242" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc2</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -40370,19 +37222,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN243" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -40538,19 +37377,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN244" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -40702,19 +37528,6 @@
           <t>https://baxtel.com/data-center/equinix-manassas-dc14</t>
         </is>
       </c>
-      <c r="AN245" t="n">
-        <v>2004</v>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-manassas-dc14</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -40864,19 +37677,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
         </is>
       </c>
-      <c r="AN246" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -41028,19 +37828,6 @@
           <t>https://baxtel.com/data-center/cloudhq-mcc3</t>
         </is>
       </c>
-      <c r="AN247" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO247" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP247" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-mcc3</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -41196,19 +37983,6 @@
           <t>https://baxtel.com/data-center/vantage-va13</t>
         </is>
       </c>
-      <c r="AN248" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO248" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP248" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/vantage-va13</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -41360,19 +38134,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN249" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO249" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP249" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -41514,19 +38275,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN250" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP250" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -41678,19 +38426,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN251" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP251" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -41842,19 +38577,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN252" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -42004,19 +38726,6 @@
           <t>https://baxtel.com/data-center/google-bristow-campus</t>
         </is>
       </c>
-      <c r="AN253" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP253" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-bristow-campus</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -42164,19 +38873,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN254" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -42328,19 +39024,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN255" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP255" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -42488,19 +39171,6 @@
         </is>
       </c>
       <c r="AM256" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
-      <c r="AN256" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
         <is>
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
@@ -42646,19 +39316,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
         </is>
       </c>
-      <c r="AN257" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP257" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-100-iad-101-iad-102-i-ad1042ec</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -42806,19 +39463,6 @@
           <t>https://baxtel.com/data-center/amazon-iad-214</t>
         </is>
       </c>
-      <c r="AN258" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP258" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad-214</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -42978,19 +39622,6 @@
           <t>https://baxtel.com/data-center/aligned-iad03</t>
         </is>
       </c>
-      <c r="AN259" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP259" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/aligned-iad03</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -43146,19 +39777,6 @@
           <t>https://baxtel.com/data-center/digital-realty-iad55</t>
         </is>
       </c>
-      <c r="AN260" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP260" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-iad55</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -43310,19 +39928,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN261" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO261" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP261" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -43474,19 +40079,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN262" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -43634,19 +40226,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN263" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -43794,19 +40373,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN264" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP264" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -43954,19 +40520,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN265" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -44114,19 +40667,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN266" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO266" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP266" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -44276,19 +40816,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-va-3</t>
         </is>
       </c>
-      <c r="AN267" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-va-3</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -44438,19 +40965,6 @@
           <t>https://baxtel.com/data-center/google-bristow-campus</t>
         </is>
       </c>
-      <c r="AN268" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO268" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-bristow-campus</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -44598,19 +41112,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN269" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO269" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -44758,19 +41259,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN270" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -44914,19 +41402,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-va-4</t>
         </is>
       </c>
-      <c r="AN271" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-va-4</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -45070,19 +41545,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-va-5</t>
         </is>
       </c>
-      <c r="AN272" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-va-5</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -45230,19 +41692,6 @@
         </is>
       </c>
       <c r="AM273" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-manassas-dc2</t>
-        </is>
-      </c>
-      <c r="AN273" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/qts-manassas-dc2</t>
         </is>
@@ -45384,19 +41833,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
         </is>
       </c>
-      <c r="AN274" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-124-125-126-127-b9b0fdeb</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -45548,19 +41984,6 @@
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
       </c>
-      <c r="AN275" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP275" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -45712,19 +42135,6 @@
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
       </c>
-      <c r="AN276" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO276" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP276" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -45872,19 +42282,6 @@
         </is>
       </c>
       <c r="AM277" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
-      <c r="AN277" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO277" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP277" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
@@ -46026,19 +42423,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN278" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO278" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP278" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -46180,19 +42564,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN279" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO279" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP279" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -46336,19 +42707,6 @@
           <t>https://baxtel.com/data-center/iron-mountain-va-6</t>
         </is>
       </c>
-      <c r="AN280" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO280" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP280" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/iron-mountain-va-6</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -46504,19 +42862,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc6</t>
         </is>
       </c>
-      <c r="AN281" t="n">
-        <v>2010</v>
-      </c>
-      <c r="AO281" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP281" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc6</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -46672,19 +43017,6 @@
           <t>https://baxtel.com/data-center/equinix-ashburn-dc4-f292a6c2-9340-43c9-821a-abfe935da89e</t>
         </is>
       </c>
-      <c r="AN282" t="n">
-        <v>2007</v>
-      </c>
-      <c r="AO282" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP282" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-ashburn-dc4-f292a6c2-9340-43c9-821a-abfe935da89e</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -46836,19 +43168,6 @@
         </is>
       </c>
       <c r="AM283" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
-        </is>
-      </c>
-      <c r="AN283" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO283" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP283" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/digital-realty-dulles-expansion</t>
         </is>
@@ -46994,19 +43313,6 @@
           <t>https://baxtel.com/news/blackchamber-plans-to-develop-a-large-data-center-campus-in-northern-virginia</t>
         </is>
       </c>
-      <c r="AN284" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO284" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP284" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/news/blackchamber-plans-to-develop-a-large-data-center-campus-in-northern-virginia</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -47148,19 +43454,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN285" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO285" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP285" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -47302,19 +43595,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN286" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO286" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP286" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -47456,19 +43736,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN287" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO287" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP287" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -47610,19 +43877,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN288" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO288" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP288" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -47764,19 +44018,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN289" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO289" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP289" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -47924,19 +44165,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
         </is>
       </c>
-      <c r="AN290" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AO290" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP290" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-shellhorn</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -48080,19 +44308,6 @@
         </is>
       </c>
       <c r="AM291" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-ashburn-campus</t>
-        </is>
-      </c>
-      <c r="AN291" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO291" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP291" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/cloudhq-ashburn-campus</t>
         </is>
@@ -48238,19 +44453,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
         </is>
       </c>
-      <c r="AN292" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO292" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP292" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -48392,19 +44594,6 @@
           <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
         </is>
       </c>
-      <c r="AN293" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO293" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP293" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-ashburn-lockridge</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -48548,19 +44737,6 @@
         </is>
       </c>
       <c r="AM294" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/vantage-va2-campus</t>
-        </is>
-      </c>
-      <c r="AN294" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO294" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP294" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/vantage-va2-campus</t>
         </is>
@@ -48652,19 +44828,6 @@
           <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
         </is>
       </c>
-      <c r="AN295" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO295" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP295" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -48752,19 +44915,6 @@
           <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
         </is>
       </c>
-      <c r="AN296" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO296" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP296" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ovh-us-east-vint-hill</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -48910,19 +45060,6 @@
           <t>https://baxtel.com/data-center/cloudhq-lc4</t>
         </is>
       </c>
-      <c r="AN297" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO297" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP297" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-lc4</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -49074,19 +45211,6 @@
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
       </c>
-      <c r="AN298" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO298" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP298" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -49234,19 +45358,6 @@
         </is>
       </c>
       <c r="AM299" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
-        </is>
-      </c>
-      <c r="AN299" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO299" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP299" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/ta-realty-leesburg</t>
         </is>
@@ -49392,19 +45503,6 @@
           <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
         </is>
       </c>
-      <c r="AN300" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO300" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP300" t="inlineStr">
-        <is>
-          <t>https://www.datacenter.fyi/public-record/amazon-data-services-inc-iad-104-105-106-86e7ab23</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -49540,19 +45638,6 @@
           <t>https://baxtel.com/data-center/coresite-reston-va3</t>
         </is>
       </c>
-      <c r="AN301" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO301" t="inlineStr">
-        <is>
-          <t>year opened</t>
-        </is>
-      </c>
-      <c r="AP301" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/coresite-reston-va3</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -49696,19 +45781,6 @@
         </is>
       </c>
       <c r="AM302" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/cloudhq-lc2</t>
-        </is>
-      </c>
-      <c r="AN302" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AO302" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP302" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/cloudhq-lc2</t>
         </is>
@@ -49854,19 +45926,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN303" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO303" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP303" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -50008,19 +46067,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN304" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO304" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP304" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -50166,19 +46212,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN305" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO305" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP305" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -50326,19 +46359,6 @@
         </is>
       </c>
       <c r="AM306" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-jacksonville-road</t>
-        </is>
-      </c>
-      <c r="AN306" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO306" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP306" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/microsoft-jacksonville-road</t>
         </is>
@@ -50482,19 +46502,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN307" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO307" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP307" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -50634,19 +46641,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN308" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO308" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP308" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -50788,19 +46782,6 @@
           <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
         </is>
       </c>
-      <c r="AN309" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AO309" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP309" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-leesburg-stonewall-park</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -50950,19 +46931,6 @@
           <t>https://baxtel.com/data-center/google-bristow-campus</t>
         </is>
       </c>
-      <c r="AN310" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO310" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP310" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/google-bristow-campus</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -51108,19 +47076,6 @@
           <t>https://baxtel.com/data-center/qts-manassas-dc1</t>
         </is>
       </c>
-      <c r="AN311" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AO311" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP311" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/qts-manassas-dc1</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -51272,19 +47227,6 @@
           <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
         </is>
       </c>
-      <c r="AN312" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AO312" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP312" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/microsoft-leesburg-3</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -51436,19 +47378,6 @@
         </is>
       </c>
       <c r="AM313" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
-        </is>
-      </c>
-      <c r="AN313" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO313" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP313" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/centersquare-ashburn-wdc1</t>
         </is>
@@ -51542,19 +47471,6 @@
           <t>https://baxtel.com/data-center/lumos-lynchburg</t>
         </is>
       </c>
-      <c r="AN314" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AO314" t="inlineStr">
-        <is>
-          <t>announcement year</t>
-        </is>
-      </c>
-      <c r="AP314" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/lumos-lynchburg</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -51698,19 +47614,6 @@
           <t>https://baxtel.com/data-center/8100-boone-digital-realty</t>
         </is>
       </c>
-      <c r="AN315" t="n">
-        <v>1992</v>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/8100-boone-digital-realty</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -51868,19 +47771,6 @@
           <t>https://baxtel.com/data-center/amazon-iad-69</t>
         </is>
       </c>
-      <c r="AN316" t="n">
-        <v>2015</v>
-      </c>
-      <c r="AO316" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP316" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/amazon-iad-69</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -52026,19 +47916,6 @@
           <t>https://baxtel.com/data-center/lumen-mclean-1</t>
         </is>
       </c>
-      <c r="AN317" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AO317" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP317" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/lumen-mclean-1</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -52188,19 +48065,6 @@
           <t>https://baxtel.com/data-center/equinix-dc22</t>
         </is>
       </c>
-      <c r="AN318" t="n">
-        <v>2025</v>
-      </c>
-      <c r="AO318" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP318" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/equinix-dc22</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -52358,19 +48222,6 @@
           <t>https://baxtel.com/data-center/ntt-va7</t>
         </is>
       </c>
-      <c r="AN319" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AO319" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP319" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va7</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -52514,19 +48365,6 @@
         </is>
       </c>
       <c r="AM320" t="inlineStr">
-        <is>
-          <t>https://baxtel.com/data-center/ntt-va11</t>
-        </is>
-      </c>
-      <c r="AN320" t="n">
-        <v>2027</v>
-      </c>
-      <c r="AO320" t="inlineStr">
-        <is>
-          <t>construction completion</t>
-        </is>
-      </c>
-      <c r="AP320" t="inlineStr">
         <is>
           <t>https://baxtel.com/data-center/ntt-va11</t>
         </is>
